--- a/Insurance Rate Data Scraper/output/ak_all_companies_search.xlsx
+++ b/Insurance Rate Data Scraper/output/ak_all_companies_search.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG436"/>
+  <dimension ref="A1:AG449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28188,6 +28188,851 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>SFMA-134887915</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>134887915</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>25143</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>HO-50001</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P437" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE437" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134887915</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>TRVD-G134901363</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>134911799</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Crime Form Filing 2026-03-0767-BT-F</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>26.0001 Commercial Burglary and Theft</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P438" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE438" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134911799</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>TRVD-G134901367</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>134911801</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Crime Form Filing 2026-03-0767-FID-F</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>23.0000 Fidelity</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P439" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE439" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134911801</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>TRVD-G134901365</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>134911800</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Crime Rule 2026-03-0767-BT-RU</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>26.0001 Commercial Burglary and Theft</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P440" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE440" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134911800</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>TRVD-G134901382</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>134911802</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Crime Rule Filing 2026-03-0767-FID-RU</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>23.0000 Fidelity</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P441" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134911802</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>TRVD-G134896163</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>134905182</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>CyberRisk Form Filing 2026-03-0743-F</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>17.0028 Cyber Liability</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P442" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134905182</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>TRVD-G134896182</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>134905183</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>CyberRisk Rule Filing 2026-03-0743-RU</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>17.0028 Cyber Liability</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P443" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134905183</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>TRVD-G134896052</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>134903581</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Directors and Officers Form Filing 2026-03-0754-F</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>17.0006 Directors &amp; Officers Liability</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P444" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE444" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134903581</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>TRVD-G134896035</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>134903582</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Directors and Officers Rule Filing 2026-03-0754-RU</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>17.0006 Directors &amp; Officers Liability</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P445" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134903582</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>TRVD-G134977919</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>134992179</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>EPL Form Filing 2026-03-0721-F</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>17.0010 Employment Practices Liability</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P446" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE446" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG446" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134992179</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>TRVD-G134977920</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>134992181</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>EPL Rule Filing 2026-03-0721-RU</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>17.0010 Employment Practices Liability</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P447" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134992181</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>TRVD-135004521</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>135004521</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Excess Follow-Form and Umbrella Liability</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Closed - Approved</t>
+        </is>
+      </c>
+      <c r="P448" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE448" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135004521</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>LINU-134932555</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>134932555</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Underwriters Inc.</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>19917</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Electronic Signature</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>35.0002 Commercial Interline Filings</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Closed - Authorized</t>
+        </is>
+      </c>
+      <c r="P449" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE449" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134932555</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
